--- a/main/CodeSystem-BloomfilterTypeCS.xlsx
+++ b/main/CodeSystem-BloomfilterTypeCS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12</t>
+    <t>2026-02-18</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright 2020-2025 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
+    <t>Copyright 2020-2026 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
   </si>
   <si>
     <t>Case Sensitive</t>
